--- a/Result/checksun_type/鋼筋.xlsx
+++ b/Result/checksun_type/鋼筋.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>27.55</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>27.55</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>0</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-30.09271433251715</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>0</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>27.28</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>27.56</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>0</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-30.09271433251715</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>0</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>27.32</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>27.58</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>82.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>0</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-30.09271433251715</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>82</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>27.36</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>27.44</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>27.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>30.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>0</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-33.0866462288709</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>30</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>27.58</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>27.61</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>27.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>112.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>0</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-30.6105972869166</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>112</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>27.61</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>27.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>0</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>0</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>27.48</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>27.64</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>27.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>0</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>0</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>27.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>0</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>0</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>27.54</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>27.67</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>27.67</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>0</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>27.68</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>27.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>0</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>27.68</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>27.68</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>0</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>0</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>13.3</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>13.83</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>14.6</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>8976090.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>4041437.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>4041437.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>3593013.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>4033863.6</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>4033863.6</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>378784.592464637</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>8976090</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>8976090.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>13.21</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>13.89</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>14.62</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>14.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1572226.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3065382.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3065382.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2933268.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>3969180.46</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>3969180.46</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-86897.960141527</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1572226</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1572226.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>13.23</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>14.65</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>3546778.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3397879.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3397879</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2964451.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>4110827.08</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>4110827.08</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>44215.89185472205</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>3546778</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>3546778.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>13.32</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>14.68</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14.68</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>4124104.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3574991.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3574991.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2919981.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>4081166.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>4081166.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>18383.11285455152</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>4124104</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>4124104.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>13.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>14.16</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>14.72</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>14.72</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1987989.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3253237.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3253237.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2668362.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>4074257.44</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>4074257.44</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-81033.75403335365</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1987989</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1987989.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>13.67</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>14.76</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14.76</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>4095817.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>3144589.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>3144589.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2764215.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>4070259.46</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>4070259.46</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>8705.677342258394</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>4095817</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>4095817.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>13.83</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>14.8</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>3234707.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2801153.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2801153.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2735467.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>4056191.86</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>4056191.86</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-89244.76631194819</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>3234707</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>3234707.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>13.91</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>14.82</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>4432342.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2531023.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2531023.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2792326.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>4047551.38</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>4047551.38</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-133724.8727353876</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>4432342</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>4432342.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>13.96</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>14.51</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>14.85</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2515334.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2264971.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2264971.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2623207.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>4071737.86</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>4071737.86</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-320810.0293140374</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2515334</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2515334.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>14.57</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>14.87</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1444747.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2083488.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2083488</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2624094.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>4110096.82</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>4110096.82</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-371223.3233794644</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1444747</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1444747.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>14.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>14.89</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>14.89</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2378637.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2383840.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2383840.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2826023.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>4162291.56</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>4162291.56</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-315278.5890665217</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2378637</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2378637.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>15.57</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>16.25</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>3184280.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1257083.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1257083.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1064711.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1194971.18</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1194971.18</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>115356.4962169959</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>3184280</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>3184280.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>15.59</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>16.27</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>531740.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>700896.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>700896.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>833401.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1151490.38</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1151490.38</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-72499.9008129671</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>531740</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>531740.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>16.32</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>16.32</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>833554.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>814799.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>814799.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>835888.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1161385.88</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1161385.88</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-54076.18582673674</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>833554</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>833554.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>16.37</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>16.37</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1131868.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>785167.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>785167.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>813053.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1159266.78</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1159266.78</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-58162.51492402435</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1131868</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1131868.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>15.59</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>15.72</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>16.42</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>603975.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>738452.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>738452.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>763557.0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1150552.12</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1150552.12</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-93885.1095300056</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>603975</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>603975.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>15.77</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>16.46</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>16.46</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>403346.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>872339.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>872339.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>836711.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1144166.26</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1144166.26</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-85004.38362676429</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>403346</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>403346.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>15.73</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>15.81</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>16.51</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1101255.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>965907.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>965907</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1038595.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1149632.4</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1149632.4</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-47785.7972068924</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1101255</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1101255.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>15.69</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>15.85</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>16.55</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>685393.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>856977.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>856977.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>989811.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1135853.02</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1135853.02</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-67685.71670682915</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>685393</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>685393.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>15.7</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>16.6</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>898294.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>840940.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>840940.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1123941.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1153041.94</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1153041.94</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-49140.18325292331</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>898294</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>898294.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>15.92</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>16.64</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>16.64</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1273408.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>788661.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>788661.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1184457.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1162483.82</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1162483.82</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-43702.37891688233</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1273408</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1273408.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>15.63</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>15.94</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>16.68</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>16.68</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>871185.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>801084.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>801084</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1164826.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1166986.14</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1166986.14</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-74564.07347550616</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>871185</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>871185.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>8.459999999999999</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>8.68</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>9.06</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>9.06</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>3737926.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2293923.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2293923.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>2665931.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>3501500.12</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>3501500.12</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-194853.3927038419</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>3737926</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>3737926.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>8.392</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>8.68</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>9.07</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>9.07</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>2147583.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2152763.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2152763.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>2767202.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>3485690.08</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>3485690.08</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-334331.4059387725</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>2147583</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>2147583.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>8.424000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>9.1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1240045.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>2238085.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>2238085.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>2732103.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>3533987.4</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>3533987.4</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-351251.4103480033</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1240045</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1240045.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>8.478</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>8.73</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>9.13</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>9.130000000000001</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2827352.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>2456676.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>2456676.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2769527.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>3551150.54</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>3551150.54</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-265641.9377059042</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2827352</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2827352.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>8.592</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>8.76</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>9.16</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>9.16</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1516712.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>2607787.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>2607787.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>2824589.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>3526108.82</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>3526108.82</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-303924.0861562658</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1516712</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1516712.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>8.704</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>8.79</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>9.19</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>9.19</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>3032126.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>3037939.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>3037939.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>3003854.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>3535828.66</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>3535828.66</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-207332.7237226302</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>3032126</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>3032126.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>8.814</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>8.82</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>9.22</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>9.220000000000001</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>2574192.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>3381641.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>3381641</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>3529049.4</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>3523707.72</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>3523707.72</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-224306.1086844858</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2574192</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2574192.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>8.848</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>9.25</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>9.25</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>2333002.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>3226121.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>3226121.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>3565981.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>3525734.58</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>3525734.58</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-191478.5118912617</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>2333002</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>2333002.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>8.874</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>8.86</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>9.27</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>9.27</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>3582905.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3082377.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3082377.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>3607678.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>3513884.48</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>3513884.48</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-111901.6410476821</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>3582905</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>3582905.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>8.866</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>8.87</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>9.29</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>9.289999999999999</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>3667473.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>3041391.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>3041391</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>3424701.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>3484834.32</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>3484834.32</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-128142.0883765803</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3667473</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3667473.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>8.854</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>8.88</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>9.31</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>9.31</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>4750633.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>2969770.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>2969770.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3585229.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>3456014.58</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>3456014.58</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-155827.0814044145</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>4750633</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>4750633.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>62.32000000000001</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>62.9</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>63.97</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>63.97</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>8704280.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>15719796.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>15719796.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>16939283.1</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>13673755.8</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>13673755.8</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>300733.1929959357</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>8704280</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>8704280.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>62.98</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>64.01</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>64.01000000000001</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>13613590.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>17803283.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>17803283</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>16874989.8</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>13822222.76</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>13822222.76</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>1103502.94642511</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>13613590</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>13613590.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>61.77999999999999</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>63.07</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>64.07</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>64.06999999999999</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>28665421.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>23370009.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>23370009.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>16069191.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>13761553.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>13761553.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>1684908.560380183</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>28665421</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>28665421.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>61.77999999999999</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>63.17</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>64.11</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>64.11</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>16299112.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>20389573.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>20389573.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>13844080.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>13405829.02</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>13405829.02</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>842616.524588136</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>16299112</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>16299112.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>62.17999999999999</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>63.25</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>64.17</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>11316581.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>19068893.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>19068893.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>13318414.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>13267845.18</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>13267845.18</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>934210.419007061</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>11316581</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>11316581.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>62.64</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>63.39</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>64.25</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>64.25</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>19121711.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>18158769.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>18158769.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>13467231.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>13228258.1</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>13228258.1</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>1565536.788926702</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>19121711</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>19121711.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>63.27999999999999</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>64.35</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>64.34999999999999</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>41447222.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>15946696.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>15946696.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>12569121.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>12937127.38</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>12937127.38</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>1575255.646350237</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>41447222</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>41447222.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>63.67999999999999</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>63.63</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>64.42</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>13763241.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>8768373.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>8768373</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>10303528.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>12259767.7</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>12259767.7</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-859138.4375572242</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>13763241</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>13763241.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>63.85999999999999</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>63.69</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>64.46</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>64.45999999999999</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>9695711.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>7298588.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>7298588</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>10025901.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>12286433.32</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>12286433.32</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-1340019.934655124</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>9695711</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>9695711.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>63.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>63.72</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>64.49</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>64.48999999999999</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>6765962.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>7567936.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>7567936.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>10961368.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>12385281.66</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>12385281.66</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-1543328.86141444</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>6765962</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>6765962.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>63.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>63.93</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>64.55</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>64.55</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>8061347.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>8775693.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>8775693.800000001</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>11351024.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>12459611.04</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>12459611.04</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-1464749.618877232</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>8061347</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>8061347.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>7.090000000000001</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>7.14</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>7.5</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>2676012.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1369442.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1369442.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1241254.0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1402994.76</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1402994.76</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>65375.25637170998</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>2676012</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>2676012.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>7.068000000000001</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>7.15</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>7.51</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>7.51</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>775885.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>988459.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>988459.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1123535.6</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1380429.96</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1380429.96</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-63382.12694243062</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>775885</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>775885.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>7.06</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>7.17</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>7.53</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>842096.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1255108.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1255108.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1151862.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1400008.14</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1400008.14</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-41472.56285754498</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>842096</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>842096.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>7.066</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>7.18</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>7.55</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>7.55</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1448260.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1233087.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1233087.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1147027.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1411228.0</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1411228</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-15786.05834851018</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1448260</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1448260.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>7.086</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>7.57</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1104959.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1086330.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1086330.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1073226.0</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1415068.54</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1415068.54</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-43473.4069660136</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1104959</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1104959.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>7.102000000000001</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>7.22</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>7.59</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>7.59</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>771097.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1113065.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1113065.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1133684.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1444365.44</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1444365.44</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-44691.89045651816</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>771097</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>771097.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>7.128</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>7.24</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>7.62</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>7.62</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2109132.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1258611.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1258611.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1163577.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1472405.4</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1472405.4</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-9065.513640934601</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2109132</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2109132.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>7.138000000000001</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>7.27</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>7.64</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>7.64</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>731991.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1048615.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1048615.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1133197.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1451525.66</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1451525.66</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-101207.8141314962</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>731991</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>731991.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>7.144</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>7.29</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>7.66</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>7.66</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>714475.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1060967.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1060967</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1217588.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>1463135.96</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>1463135.96</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-81674.28575617354</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>714475</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>714475.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,21 +28577,17 @@
           <t>7.154000000000001</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>7.31</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
+      <c r="AM66" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="AO66" t="inlineStr">
         <is>
           <t>7.68</t>
         </is>
       </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>7.68</t>
-        </is>
-      </c>
       <c r="AP66" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -29016,20 +28628,16 @@
           <t>1238633.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1060121.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1060121.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1282014.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>1475423.72</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>1475423.72</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-48975.59215727774</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1238633</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1238633.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>7.182</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>7.33</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>7.7</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1498828.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1154304.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1154304</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1233965.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1480312.72</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1480312.72</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-56673.83015323849</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1498828</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1498828.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
